--- a/output/full_scan/batch_seq7_2026-10-01.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-01.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6532</v>
+        <v>6743</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>969</v>
+        <v>1172.529699639857</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>122.5</v>
+        <v>33.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>81.14049728499099</v>
+        <v>83.75108953250931</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43.34917140364297</v>
+        <v>27.57514192331467</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.362479966831288</v>
+        <v>2.852969963985754</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.125984010382004</v>
+        <v>0.3559228852363628</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6771</v>
+        <v>6532</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>926.8127451031696</v>
+        <v>1169</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43</v>
+        <v>122.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.43954312431521</v>
+        <v>81.14049744143438</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>22.34750097460934</v>
+        <v>43.34917154126512</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.848792546824556</v>
+        <v>5.362479966831288</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.811371226418284e-05</v>
+        <v>2.12598400924702</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6491</v>
+        <v>6691</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>883.4645431270836</v>
+        <v>1168.192464257687</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>421.5</v>
+        <v>733</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>68.99121187346387</v>
+        <v>68.83827289870584</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.40103604394995</v>
+        <v>21.33429801664045</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.946454312708361</v>
+        <v>2.419246425768741</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.108848029881322</v>
+        <v>14.19097712572169</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6672</v>
+        <v>6491</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>865.0056141001203</v>
+        <v>1133.464543127084</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>405.5</v>
+        <v>421.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>79.8988772224379</v>
+        <v>68.99121177826206</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.68769623406891</v>
+        <v>30.4010360500244</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.651561809958198</v>
+        <v>1.946454312708361</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>8.642863078270139</v>
+        <v>2.108848030882761</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6743</v>
+        <v>6672</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>862.5296996398575</v>
+        <v>1085.00561410012</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33.5</v>
+        <v>405.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>83.75108955331153</v>
+        <v>79.89887722547097</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.5751418799443</v>
+        <v>33.68769626631069</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.852969963985754</v>
+        <v>2.651561809958198</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3559228852474912</v>
+        <v>8.642863078314626</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6834</v>
+        <v>6771</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>855.9998459454265</v>
+        <v>1041.81274510317</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>119.5</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>64.09219155231489</v>
+        <v>66.43954291351852</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.07279087824212</v>
+        <v>22.34750110003345</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.503879169312211</v>
+        <v>1.848792546824556</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.243958667841978</v>
+        <v>7.811377902366967e-05</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6691</v>
+        <v>6834</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>853.1924642576874</v>
+        <v>1040.999845945427</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>733</v>
+        <v>119.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.83827294597887</v>
+        <v>64.09219155585248</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.33429798678431</v>
+        <v>34.07279100097263</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.419246425768741</v>
+        <v>1.503879169312211</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>14.19097712394142</v>
+        <v>1.243958667764082</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6488</v>
+        <v>6695</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>778.7746656392045</v>
+        <v>981.7251533261516</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1085</v>
+        <v>55.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.02050108921804</v>
+        <v>69.37046288189025</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.35232927661964</v>
+        <v>22.08721615890254</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.188011523012727</v>
+        <v>1.863751636714938</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>16.27310923805928</v>
+        <v>0.8988244782071823</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6716</v>
+        <v>6488</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>771.8375296419183</v>
+        <v>978.7746656392056</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>117.5</v>
+        <v>1085</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>51.002303734153</v>
+        <v>64.02050112138366</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.48961079011585</v>
+        <v>12.35232945657344</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5913716749696126</v>
+        <v>2.188011523012727</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.957581031712856</v>
+        <v>16.27310923527759</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6538</v>
+        <v>6533</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>747.6358236616909</v>
+        <v>930.8439464981916</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>369.5</v>
+        <v>366.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.23023783978353</v>
+        <v>80.05015596593303</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>56.232011213584</v>
+        <v>29.90990474148475</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7266694696932742</v>
+        <v>4.684394649819157</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-7.468305502670056</v>
+        <v>11.02592535318758</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6533</v>
+        <v>6706</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>730.8439464981916</v>
+        <v>930.356610207123</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>366.5</v>
+        <v>154.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>80.05015597665567</v>
+        <v>61.57444712134245</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>29.90990468675808</v>
+        <v>48.0490144497028</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.684394649819157</v>
+        <v>0.9921150321653142</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>11.02592535341011</v>
+        <v>0.5794081928333998</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6805</v>
+        <v>6708</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>726.0970825793235</v>
+        <v>914</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2390</v>
+        <v>56.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.89632025045417</v>
+        <v>72.40671562031883</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.6223780231586</v>
+        <v>14.30526551870728</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.546901754909257</v>
+        <v>8.971264226837246</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>5.284969655734898</v>
+        <v>1.679122416742374</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6708</v>
+        <v>6799</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>714</v>
+        <v>907.263373705536</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>56.8</v>
+        <v>92.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>72.40671563513368</v>
+        <v>70.09539128665867</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.30526541323645</v>
+        <v>26.67661116707594</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.971264226837246</v>
+        <v>1.355003301669034</v>
       </c>
       <c r="K14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.679122416809138</v>
+        <v>1.479276315332369</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6683</v>
+        <v>6505</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>703.7199846508976</v>
+        <v>878.8122009832589</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1575</v>
+        <v>94.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.54885393227951</v>
+        <v>67.30779089592889</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.67953434237804</v>
+        <v>50.10234387633921</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7215067713222314</v>
+        <v>0.9922812122559262</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.457694497360492</v>
+        <v>0.8449883398862879</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6695</v>
+        <v>6579</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>691.7251533261515</v>
+        <v>876.6825147063815</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>55.4</v>
+        <v>160.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>69.37046302609414</v>
+        <v>62.51536301691801</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.08721608127721</v>
+        <v>17.04284969253934</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.863751636714938</v>
+        <v>0.7906415392221861</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.8988244781404164</v>
+        <v>1.536930949303615</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6811</v>
+        <v>6485</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>685.2530024145509</v>
+        <v>864</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>243.5</v>
+        <v>84.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.92315711993398</v>
+        <v>77.23355876114292</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.84426812358081</v>
+        <v>29.94483657824696</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4078215654634888</v>
+        <v>5.229929527807045</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.4805445338868583</v>
+        <v>2.266664417349901</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6577</v>
+        <v>6805</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>675.1580220429204</v>
+        <v>856.2682930891576</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>80.5</v>
+        <v>2390</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.4105059388432</v>
+        <v>57.89632023874583</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.40474218277494</v>
+        <v>34.62237796603343</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.542305221201483</v>
+        <v>1.568047208230094</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1237869807623939</v>
+        <v>5.28496966018551</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6530</v>
+        <v>6789</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>672.2344525663757</v>
+        <v>813.6224227020272</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>102</v>
+        <v>489</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.01106607147232</v>
+        <v>60.46161219806217</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.46280099279971</v>
+        <v>14.8754075937118</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6202301277519832</v>
+        <v>1.174856388325669</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1149238585973564</v>
+        <v>4.443282385513916</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6485</v>
+        <v>6770</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>664</v>
+        <v>807.2814401298699</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>84.7</v>
+        <v>74.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>77.23355878077975</v>
+        <v>56.7731353332136</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.94483657984828</v>
+        <v>9.905080349130136</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5.229929527807045</v>
+        <v>0.7696810047793432</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.266664417216369</v>
+        <v>0.2316780584175688</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6706</v>
+        <v>6530</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>655.356610207123</v>
+        <v>787.2344525663757</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>154.5</v>
+        <v>102</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.57444716366949</v>
+        <v>60.01106608684299</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>48.04901445766432</v>
+        <v>33.46280102005623</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9921150321653142</v>
+        <v>0.6202301277519832</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5794081931671862</v>
+        <v>0.1149238584415854</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6668</v>
+        <v>6643</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>630.1323622414224</v>
+        <v>785.2240614488785</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>47.1</v>
+        <v>521</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.72280695164162</v>
+        <v>62.96886608440963</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45.97966980755234</v>
+        <v>30.27383170348095</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5299446892389362</v>
+        <v>2.322406144887854</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0659377853613194</v>
+        <v>11.31785404426699</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6799</v>
+        <v>6693</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>627.263373705536</v>
+        <v>781.9234071760386</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92.2</v>
+        <v>212.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>70.09539137290506</v>
+        <v>64.13583893938227</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.67661115850517</v>
+        <v>23.14823069968008</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.355003301669034</v>
+        <v>0.9923407176038604</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.479276315287867</v>
+        <v>4.061493785467544</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6643</v>
+        <v>6658</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>615.2240614488785</v>
+        <v>779.599045813515</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>521</v>
+        <v>181</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.96886604937493</v>
+        <v>59.18825151653689</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>30.27383170348095</v>
+        <v>20.23811637040868</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.322406144887854</v>
+        <v>0.5617023218681989</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>11.31785404716007</v>
+        <v>0.8323675279038336</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6642</v>
+        <v>6716</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>608.9542156390036</v>
+        <v>771.8375296419183</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>83</v>
+        <v>117.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.10053333449422</v>
+        <v>51.00230370134203</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.14851487570813</v>
+        <v>25.48961071945976</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.4930382935012</v>
+        <v>0.5913716749696126</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>3</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6130247516651119</v>
+        <v>-0.9575810318797632</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6505</v>
+        <v>6642</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>593.8122009832589</v>
+        <v>748.9542156390036</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>94.2</v>
+        <v>83</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>67.30779086772716</v>
+        <v>61.10053337564455</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>50.10234390228977</v>
+        <v>19.14851499095617</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9922812122559262</v>
+        <v>2.4930382935012</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.8449883400198193</v>
+        <v>0.6130247513535563</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6588</v>
+        <v>6538</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>585.6425291758087</v>
+        <v>747.6358236616909</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>110</v>
+        <v>369.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.00658135809372</v>
+        <v>59.23023784312416</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.6674581459727</v>
+        <v>56.23201130189531</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4392867406270277</v>
+        <v>0.7266694696932742</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.011937941953205</v>
+        <v>-7.468305502914802</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6693</v>
+        <v>6683</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>581.9234071760386</v>
+        <v>703.7199846508976</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>212.5</v>
+        <v>1575</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.13583895261289</v>
+        <v>58.54885393744125</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.14823073366732</v>
+        <v>20.67953444762518</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9923407176038604</v>
+        <v>0.7215067713222314</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>4.061493785489807</v>
+        <v>2.457694495468786</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6658</v>
+        <v>6811</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>564.5990458135152</v>
+        <v>685.2530024145509</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>181</v>
+        <v>243.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.18825154927634</v>
+        <v>53.92315708573816</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.23811638202582</v>
+        <v>29.84426809970641</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5617023218681989</v>
+        <v>0.4078215654634888</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.8323675278815825</v>
+        <v>-0.4805445334417877</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6690</v>
+        <v>6654</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>563.5449504184753</v>
+        <v>679.0817166247713</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.60573159581794</v>
+        <v>57.18943743978311</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.71481822209445</v>
+        <v>23.64124205312764</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3296956338997165</v>
+        <v>0.9893979459960108</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.2268310328210283</v>
+        <v>-0.4190872182785448</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6770</v>
+        <v>6577</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>562.2814401298699</v>
+        <v>675.1580220429204</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>74.5</v>
+        <v>80.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.77313533181926</v>
+        <v>55.41050582537157</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9.905080329667252</v>
+        <v>11.40474219541703</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7696810047793432</v>
+        <v>1.542305221201483</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2316780584064334</v>
+        <v>0.1237869805175917</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6789</v>
+        <v>6666</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>558.6224227020265</v>
+        <v>670.1309496784187</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>489</v>
+        <v>45.95</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.46161218768646</v>
+        <v>65.49494371726838</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.87540758149788</v>
+        <v>8.633175724921928</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.174856388325669</v>
+        <v>0.0519125742109915</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.44328238640411</v>
+        <v>0.1029363100627694</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6666</v>
+        <v>6664</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>555.1309496784187</v>
+        <v>669.8913613167022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45.95</v>
+        <v>371.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.49494327186643</v>
+        <v>61.16683321467524</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8.633175701876867</v>
+        <v>14.87054227713328</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.0519125742109915</v>
+        <v>0.918974096143257</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1029363103520771</v>
+        <v>4.033361821341501</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6579</v>
+        <v>6715</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>551.6825147063814</v>
+        <v>664.3625840787475</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>160.5</v>
+        <v>453</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>62.51536292552586</v>
+        <v>61.54552297459162</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.04284935766792</v>
+        <v>23.00119411381015</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7906415392221861</v>
+        <v>0.2706575497726372</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.536930950527582</v>
+        <v>9.190620981945496</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6667</v>
+        <v>6668</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>550.2720761264077</v>
+        <v>630.1323622414224</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>261</v>
+        <v>47.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>63.25010185846842</v>
+        <v>60.72280705967434</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>39.30142119379307</v>
+        <v>45.97966983286699</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.810719030180728</v>
+        <v>0.5299446892389362</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.342802777343331</v>
+        <v>0.065937785327943</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6589</v>
+        <v>6525</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>543.3890472247801</v>
+        <v>629.4726456724028</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>52.4</v>
+        <v>136.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>57.17578764934496</v>
+        <v>52.58728653373956</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.40127129597861</v>
+        <v>11.75473573262611</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8062934393356984</v>
+        <v>0.8955181557038309</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3342663021816647</v>
+        <v>1.1152490644825</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6651</v>
+        <v>6558</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>541.1372670047605</v>
+        <v>619.213948815394</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>147.5</v>
+        <v>25.35</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.63614207713855</v>
+        <v>56.31164668202907</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.489796965797</v>
+        <v>26.31725527011924</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4705988180584011</v>
+        <v>0.671254353269776</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2402929103102424</v>
+        <v>0.2588539279703807</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6654</v>
+        <v>6640</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>539.0817166247713</v>
+        <v>616.1888018165444</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>210</v>
+        <v>1110</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.1894374378363</v>
+        <v>51.91056761477186</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.64124205312764</v>
+        <v>19.41505801788946</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9893979459960108</v>
+        <v>1.238621842220064</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4190872182340266</v>
+        <v>-14.83152574369631</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6486</v>
+        <v>6605</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>535.9703663910773</v>
+        <v>589.3130506901402</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>81.3</v>
+        <v>139</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.46063788471602</v>
+        <v>53.94904825994305</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>47.31627015566445</v>
+        <v>13.99893289323636</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2313359304725577</v>
+        <v>1.045679502187546</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1705121820041463</v>
+        <v>0.0618334099506358</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6548</v>
+        <v>6588</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>535.8278143464199</v>
+        <v>585.6425291758087</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>71.5</v>
+        <v>110</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.46216329916886</v>
+        <v>52.00658137108539</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13.76624440963866</v>
+        <v>22.66745814508242</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.48624621256323</v>
+        <v>0.4392867406270277</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,51 +2584,51 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0423408379218958</v>
+        <v>-1.011937942131242</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6806</v>
+        <v>6552</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>580.0565780427488</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3.51</v>
+        <v>25.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>31.69501767423766</v>
+        <v>58.85890982173024</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>32.59322463695786</v>
+        <v>17.83143643251422</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.5074687125205638</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.411282096651703</v>
+        <v>0.2103914246449569</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6671</v>
+        <v>6742</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>526.3726971200881</v>
+        <v>576.5785509965222</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>22.85</v>
+        <v>55.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.33022294142177</v>
+        <v>66.87082045559936</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.3306181254333</v>
+        <v>45.62142513723453</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.847384321140597</v>
+        <v>0.7923341965334267</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.000267469885279</v>
+        <v>0.8462650735466348</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6782</v>
+        <v>6690</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>502.1404847896029</v>
+        <v>563.5449504184753</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>237.5</v>
+        <v>177</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.83890454148352</v>
+        <v>55.60573160578983</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.99068187020553</v>
+        <v>33.71481824784615</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7733456113982859</v>
+        <v>0.3296956338997165</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.000768337247472</v>
+        <v>-0.2268310328210283</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6664</v>
+        <v>6667</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>499.8913613167026</v>
+        <v>550.2720761264075</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>371.5</v>
+        <v>261</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>61.16683327391615</v>
+        <v>63.25010177477331</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.87054230344039</v>
+        <v>39.30142133628678</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.918974096143257</v>
+        <v>0.810719030180728</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>4.033361820785191</v>
+        <v>1.342802777454612</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6674</v>
+        <v>6732</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>483.6763036298824</v>
+        <v>546.5349541370434</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>18.35</v>
+        <v>152</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>71.1927841504933</v>
+        <v>52.76790309861649</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>34.67675295678261</v>
+        <v>14.79406800406383</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6676303629882354</v>
+        <v>0.6882987017596683</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2379990700636499</v>
+        <v>1.066622346616725</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6807</v>
+        <v>6831</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>460.2123450223025</v>
+        <v>544.4663476087547</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>32.3</v>
+        <v>474.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.07771885047186</v>
+        <v>32.75788512427471</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13.81948287436155</v>
+        <v>23.06263954363778</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.76846778597981</v>
+        <v>0.8417199575341354</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1835429880564578</v>
+        <v>-4.113678210120703</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6558</v>
+        <v>6589</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>459.2139488154016</v>
+        <v>543.38904722478</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>25.35</v>
+        <v>52.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.31164678753046</v>
+        <v>57.17578757787877</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>26.31725522144064</v>
+        <v>21.40127126607627</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.671254353269776</v>
+        <v>0.8062934393356984</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2588539279481258</v>
+        <v>0.3342663022261767</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6640</v>
+        <v>6651</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>446.1888018165442</v>
+        <v>541.1372670047604</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1110</v>
+        <v>147.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.91056763483128</v>
+        <v>52.63614215035133</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.41505803350873</v>
+        <v>18.48979740495986</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.238621842220064</v>
+        <v>0.4705988180584011</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-14.83152574369631</v>
+        <v>-0.2402929114897256</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6742</v>
+        <v>6689</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>436.5785509965221</v>
+        <v>538.7622041234922</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>55.6</v>
+        <v>64.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>66.87082050066931</v>
+        <v>51.03777818637488</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45.62142509455821</v>
+        <v>24.17974388831313</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7923341965334267</v>
+        <v>0.1532131113362924</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.8462650736801556</v>
+        <v>-0.182382186788472</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6732</v>
+        <v>6486</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>431.5349541370435</v>
+        <v>535.9703663910773</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>152</v>
+        <v>81.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.76790283609238</v>
+        <v>58.4606378559043</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.79406790895655</v>
+        <v>47.3162702294584</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6882987017596683</v>
+        <v>0.2313359304725577</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.066622347729442</v>
+        <v>-0.1705121819818976</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6689</v>
+        <v>6548</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>428.7622041234921</v>
+        <v>535.8278143464199</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>64.2</v>
+        <v>71.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.03777821597281</v>
+        <v>47.46216330123934</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.17974392532846</v>
+        <v>13.76624451846098</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.1532131113362924</v>
+        <v>1.48624621256323</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,48 +3167,48 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1823821868774863</v>
+        <v>-0.0423408380331662</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6727</v>
+        <v>6806</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>423.1701021852188</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>488</v>
+        <v>3.51</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.03600533716821</v>
+        <v>31.69502031830342</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.50747714056764</v>
+        <v>32.59322311039604</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4875668890398835</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-4.354035540190153</v>
+        <v>0.411282038272601</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6605</v>
+        <v>6671</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>419.3130506901402</v>
+        <v>526.3726971200882</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>139</v>
+        <v>22.85</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.94904833857209</v>
+        <v>47.33022286918497</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.99893294250881</v>
+        <v>18.33061811978526</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.045679502187546</v>
+        <v>1.847384321140597</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0618334100619395</v>
+        <v>0.0002674698630253</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6830</v>
+        <v>6725</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>416.4094335515505</v>
+        <v>525.8824738521132</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>531</v>
+        <v>221</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.67529763188056</v>
+        <v>47.17615750100997</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.93806117244532</v>
+        <v>19.88387114691853</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4075796546748941</v>
+        <v>1.768079192910899</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-7.511802667660682</v>
+        <v>2.061840710735442</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6781</v>
+        <v>6782</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>413.0916411121698</v>
+        <v>522.140484789603</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1025</v>
+        <v>237.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>47.41053783501734</v>
+        <v>53.8389045738881</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.70623018353931</v>
+        <v>21.99068190740425</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5513929142900619</v>
+        <v>0.7733456113982859</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.175340151683006</v>
+        <v>-1.000768337358747</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6725</v>
+        <v>6504</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>410.8824738521132</v>
+        <v>520.1437916451212</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>221</v>
+        <v>37.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.17615750734856</v>
+        <v>49.11141284241161</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.88387114232966</v>
+        <v>25.74137693448181</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.768079192910899</v>
+        <v>0.4728523342602078</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.061840711069276</v>
+        <v>0.0348282496115244</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6669</v>
+        <v>6674</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>407.1331764522391</v>
+        <v>503.6763036298824</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2110</v>
+        <v>18.35</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>25.99530302701523</v>
+        <v>71.19278427812</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46.36036279439377</v>
+        <v>34.67675296529725</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2711680520327044</v>
+        <v>0.6676303629882354</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>85.01033259259498</v>
+        <v>0.2379990701860476</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6504</v>
+        <v>6781</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>405.143791645121</v>
+        <v>488.0916411121697</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>37.2</v>
+        <v>1025</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.11141281223909</v>
+        <v>47.41053770078109</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.74137693448181</v>
+        <v>12.70623021468588</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4728523342602078</v>
+        <v>0.5513929142900619</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0348282498340711</v>
+        <v>1.175340157246701</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6525</v>
+        <v>6684</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>404.4726456724029</v>
+        <v>483.2309898191447</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>136.5</v>
+        <v>50.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.58728653136593</v>
+        <v>60.41193695761474</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>11.75473572391052</v>
+        <v>25.16807234273296</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8955181557038309</v>
+        <v>1.029855337896197</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.11524906450477</v>
+        <v>0.5098410275566256</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6568</v>
+        <v>6679</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>401.6305069296853</v>
+        <v>468.2174756440386</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>140</v>
+        <v>204.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.36049193303253</v>
+        <v>51.76599577335996</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.41456102430818</v>
+        <v>13.01545950798069</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4893080793917935</v>
+        <v>0.4271305623362901</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.7043780624497626</v>
+        <v>1.636730953317596</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6657</v>
+        <v>6807</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>386.8447225004331</v>
+        <v>460.2123450223027</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.16401610991277</v>
+        <v>51.0777188471747</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.81413392352635</v>
+        <v>13.81948278923125</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2524070502148322</v>
+        <v>1.76846778597981</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1819855746003743</v>
+        <v>0.1835429880342025</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6494</v>
+        <v>6645</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>384.8922561258045</v>
+        <v>454.2561092212554</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>52.4</v>
+        <v>12.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.25539435490718</v>
+        <v>50.95303032065527</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.36098753943425</v>
+        <v>28.80539363006654</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.047293174155279</v>
+        <v>0.2809768051966413</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.2007859499711827</v>
+        <v>0.0589779663237003</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6510</v>
+        <v>6739</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>379.8671918447525</v>
+        <v>452.8118600802638</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>3000</v>
+        <v>1105</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.18284196898089</v>
+        <v>49.97706935725956</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.41280947049067</v>
+        <v>9.540243368781862</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8867191844752494</v>
+        <v>0.4342492334850353</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-67.95239407841237</v>
+        <v>-5.16764507725777</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6606</v>
+        <v>6550</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>377.1618231651762</v>
+        <v>435.296985473452</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.47104422901764</v>
+        <v>80.90086796747248</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>27.14443595467468</v>
+        <v>26.02111442827191</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4399043522251304</v>
+        <v>0.3497597817373697</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0267508522121129</v>
+        <v>0.9028496945073036</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6570</v>
+        <v>6735</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>374.3949583628823</v>
+        <v>430.8121371936942</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>47.55</v>
+        <v>66.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.38464959901771</v>
+        <v>59.39730227299524</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>25.50846502168285</v>
+        <v>19.99864815206276</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.637430864850178</v>
+        <v>0.935428883492572</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1743596757479286</v>
+        <v>0.8468294822573448</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6792</v>
+        <v>6830</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>373.2036461541957</v>
+        <v>426.4094335515505</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>59</v>
+        <v>531</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.17570605620565</v>
+        <v>50.67529763618585</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>24.82451587820266</v>
+        <v>24.93806119011335</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3603491547536125</v>
+        <v>0.4075796546748941</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0473231237393111</v>
+        <v>-7.51180266799452</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6684</v>
+        <v>6727</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>368.2309898191447</v>
+        <v>423.1701021852188</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>50.1</v>
+        <v>488</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>60.41193698424677</v>
+        <v>51.03600533716821</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.16807228576106</v>
+        <v>16.50747714056764</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.029855337896197</v>
+        <v>0.4875668890398835</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.50984102771241</v>
+        <v>-4.354035540190153</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6692</v>
+        <v>6568</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>366.6358417679356</v>
+        <v>401.6305069296853</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>23.05</v>
+        <v>140</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.77565071554919</v>
+        <v>52.36049194392079</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8.257327724436516</v>
+        <v>20.41456109965175</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3453429410194822</v>
+        <v>0.4893080793917935</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2994302308679961</v>
+        <v>0.7043780617821216</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6756</v>
+        <v>6669</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>364.2612697859879</v>
+        <v>397.4342604717922</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>98</v>
+        <v>2110</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.07871115768577</v>
+        <v>25.99530313075554</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.72137357254483</v>
+        <v>46.36036277727053</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.042354501496013</v>
+        <v>0.2927242696777369</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1419574646550017</v>
+        <v>85.01033261039856</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6831</v>
+        <v>6768</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>359.4663476087547</v>
+        <v>393.4957474260456</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>474.5</v>
+        <v>63.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>32.75788509640275</v>
+        <v>46.58838735595513</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.06263951444517</v>
+        <v>21.41921772225313</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8417199575341354</v>
+        <v>0.4950989722116482</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-4.113678209564384</v>
+        <v>0.2861820307476765</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6531</v>
+        <v>6657</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>357.9120170670019</v>
+        <v>386.8447225004329</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>933</v>
+        <v>32.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.80493019637875</v>
+        <v>49.1640160721287</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.102923667319864</v>
+        <v>20.8141339718448</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5219847461575761</v>
+        <v>0.2524070502148322</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-5.65789363106849</v>
+        <v>-0.1819855744445963</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6679</v>
+        <v>6494</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>353.2174756440386</v>
+        <v>384.8922561258045</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>204.5</v>
+        <v>52.4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.76599576211395</v>
+        <v>51.25539433951118</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.01545953851082</v>
+        <v>12.3609878629497</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4271305623362901</v>
+        <v>1.047293174155279</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.636730954652864</v>
+        <v>0.2007859497931515</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6591</v>
+        <v>6510</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>341.58265000285</v>
+        <v>379.8671918447525</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>43.1</v>
+        <v>3000</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.79216451141773</v>
+        <v>43.18284197412932</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>28.8997138920978</v>
+        <v>27.41280946644214</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.593799348912422</v>
+        <v>0.8867191844752494</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1344704102119344</v>
+        <v>-67.95239407952499</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6645</v>
+        <v>6606</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>339.2561092212555</v>
+        <v>377.1618231651763</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>12.75</v>
+        <v>25</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.95303022802789</v>
+        <v>43.47104413959328</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>28.80539364014035</v>
+        <v>27.14443592788982</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2809768051966413</v>
+        <v>0.4399043522251304</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.058977966301446</v>
+        <v>-0.0267508521676013</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6739</v>
+        <v>6570</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>337.8118600802645</v>
+        <v>374.3949583628823</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1105</v>
+        <v>47.55</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.97706935119242</v>
+        <v>41.38464962184764</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9.540243332671391</v>
+        <v>25.50846532335265</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4342492334850353</v>
+        <v>1.637430864850178</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.167645076256125</v>
+        <v>0.1743596755365131</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6763</v>
+        <v>6792</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>336.9794229359007</v>
+        <v>373.2036461541956</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>41.2</v>
+        <v>59</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.95049213971061</v>
+        <v>50.17570599899554</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.50673219458965</v>
+        <v>24.82451600809704</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6309975591070252</v>
+        <v>0.3603491547536125</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0812353075514374</v>
+        <v>-0.0473231235612882</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6741</v>
+        <v>6592</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>335.2398407164161</v>
+        <v>370.9459334998419</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>55.6</v>
+        <v>57</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.24551409999427</v>
+        <v>25.39465335399909</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.09377714941316</v>
+        <v>26.24459565930819</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6137755997572177</v>
+        <v>1.619949885341784</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.4915787210685368</v>
+        <v>-0.2730754126912538</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6655</v>
+        <v>6692</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>332.2556155934427</v>
+        <v>366.635841767936</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>36.26369483085548</v>
+        <v>50.77565073965482</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.45504455185799</v>
+        <v>8.257327699416296</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.0336195210122006</v>
+        <v>0.3453429410194822</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-7.90160608023372</v>
+        <v>0.2994302307456</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6552</v>
+        <v>6756</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>330.0565780427489</v>
+        <v>364.2612697859879</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>25.1</v>
+        <v>98</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>58.85890981254526</v>
+        <v>50.07871108940782</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.83143643251422</v>
+        <v>11.72137364716413</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5074687125205638</v>
+        <v>1.042354501496013</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2103914246227067</v>
+        <v>0.1419574643434478</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6585</v>
+        <v>6531</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>316.6620111767367</v>
+        <v>357.912017067002</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>102.5</v>
+        <v>933</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>34.97148122874339</v>
+        <v>49.80493021273194</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>32.63861480259598</v>
+        <v>9.10292375046663</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.00542090716276</v>
+        <v>0.5219847461575761</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1701741379758399</v>
+        <v>-5.657893632960036</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6598</v>
+        <v>6823</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>310.1453101430232</v>
+        <v>344.7352630078595</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>26.65</v>
+        <v>60.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.82563775622354</v>
+        <v>49.13346388552132</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.59529812767416</v>
+        <v>23.49077802458288</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.624298171310205</v>
+        <v>0.21066979064845</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1164286430427323</v>
+        <v>0.3536057484379116</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6560</v>
+        <v>6591</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>306.0381772712045</v>
+        <v>341.5826500028513</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>32.6</v>
+        <v>43.1</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.78409314826376</v>
+        <v>47.79216457832473</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.02695595737906</v>
+        <v>28.89971393584081</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.710867423557584</v>
+        <v>0.593799348912422</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0115143117264027</v>
+        <v>0.1344704105679962</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6670</v>
+        <v>6763</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>301.7349443873429</v>
+        <v>336.9794229359054</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>271</v>
+        <v>41.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.05390525045966</v>
+        <v>45.95049201398975</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.79887039451552</v>
+        <v>15.50673214247528</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.24188559625725</v>
+        <v>0.6309975591070252</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.6576141471353694</v>
+        <v>0.0812353074179074</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6512</v>
+        <v>6741</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>301.7224619913599</v>
+        <v>335.2398407164161</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>20.25</v>
+        <v>55.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.12765401425694</v>
+        <v>38.24551379251743</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7.783489490522946</v>
+        <v>26.09377758707795</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.075166586071519</v>
+        <v>0.6137755997572177</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2166855251411867</v>
+        <v>-0.4915787204454189</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6641</v>
+        <v>6655</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>297.8467012099453</v>
+        <v>332.2556155934428</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.83548692774394</v>
+        <v>36.26369483209665</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8.599188029717501</v>
+        <v>13.45504461413929</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4768054037945763</v>
+        <v>0.0336195210122006</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2394572761514625</v>
+        <v>-7.90160608023372</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6592</v>
+        <v>6585</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>295.9459334998422</v>
+        <v>316.6620111767367</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>57</v>
+        <v>102.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>25.39465318333836</v>
+        <v>34.97148117173559</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26.24459549247035</v>
+        <v>32.6386149011247</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.619949885341784</v>
+        <v>1.00542090716276</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2730754127135049</v>
+        <v>0.1701741378423187</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6597</v>
+        <v>6788</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>292.4535811343283</v>
+        <v>313.0030345195073</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>63</v>
+        <v>346.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.31607339832527</v>
+        <v>51.17283963366416</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6.723054246091602</v>
+        <v>12.82535160760482</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>8.02236948440278</v>
+        <v>0.6883770221731007</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>2.165018878279607</v>
+        <v>2.205716393623359</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6719</v>
+        <v>6598</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>292.2337407000568</v>
+        <v>310.1453101430232</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>188</v>
+        <v>26.65</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.46812252103225</v>
+        <v>41.8256377275477</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.72631275933851</v>
+        <v>14.59529813954081</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.020368621232586</v>
+        <v>1.624298171310205</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>1.686523917227538</v>
+        <v>-0.1164286430649847</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6561</v>
+        <v>6560</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>291.5107556246664</v>
+        <v>306.0381772712045</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>310.5</v>
+        <v>32.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.23336590353473</v>
+        <v>51.78409297171587</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.08545657588278</v>
+        <v>12.02695583133638</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8859466247272106</v>
+        <v>0.710867423557584</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.4040928989942633</v>
+        <v>0.0115143125498126</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6735</v>
+        <v>6670</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>290.8121371936941</v>
+        <v>301.7349443873429</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>66.8</v>
+        <v>271</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>59.39730224662048</v>
+        <v>48.05390532231879</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.99864798009922</v>
+        <v>20.7988705791363</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.935428883492572</v>
+        <v>1.24188559625725</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8468294826467962</v>
+        <v>-0.6576141490269634</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6768</v>
+        <v>6512</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>278.4957474260456</v>
+        <v>301.7224619913599</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>63.3</v>
+        <v>20.25</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.58838786907146</v>
+        <v>52.1276540150813</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>21.41921738423597</v>
+        <v>7.783489462389166</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4950989722116482</v>
+        <v>1.075166586071519</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2861820297462372</v>
+        <v>0.216685525130059</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6835</v>
+        <v>6796</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>277.0969401642764</v>
+        <v>298.6959459742275</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>31.15</v>
+        <v>53.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.8573036028844</v>
+        <v>44.24756767657837</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.74088883495076</v>
+        <v>23.18401872357633</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6655791190864601</v>
+        <v>0.2543796957155732</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0745170011588687</v>
+        <v>0.2166773182671839</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6803</v>
+        <v>6641</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>274.0928879027684</v>
+        <v>297.8467012099453</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>267</v>
+        <v>16.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.8846567210084</v>
+        <v>50.83548692064632</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.80335169332545</v>
+        <v>8.599187892307</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8207950515756545</v>
+        <v>0.4768054037945763</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0691633641101836</v>
+        <v>0.2394572761514625</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6584</v>
+        <v>6821</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>268.704497675622</v>
+        <v>296.1333239794246</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>531</v>
+        <v>42.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.08637357490655</v>
+        <v>53.56291238495943</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.81268361170082</v>
+        <v>15.52066973296164</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5834847122589585</v>
+        <v>0.8641457317179769</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-4.292154627758226</v>
+        <v>0.3262501866427469</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6829</v>
+        <v>6597</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>267.3459573926071</v>
+        <v>292.4535811343279</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.74788407986845</v>
+        <v>51.31607340089136</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.28141096532364</v>
+        <v>6.723054239971105</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5229788857527479</v>
+        <v>8.02236948440278</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-2.723933770198998</v>
+        <v>2.165018877901282</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6556</v>
+        <v>6719</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>259.7686138750226</v>
+        <v>292.2337407000568</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>61.6</v>
+        <v>188</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.01964922450659</v>
+        <v>48.46812248304931</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7.793949644977172</v>
+        <v>18.72631271242908</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.162475233687118</v>
+        <v>1.020368621232586</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1914498442361295</v>
+        <v>1.68652391700498</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6753</v>
+        <v>6561</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>253.9791472728554</v>
+        <v>291.5107556246665</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>133</v>
+        <v>310.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.83465976736787</v>
+        <v>41.23336552100877</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.41680134090292</v>
+        <v>23.08545693941235</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4843935688369206</v>
+        <v>0.8859466247272106</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0869811080593296</v>
+        <v>-0.4040928971026511</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6541</v>
+        <v>6835</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>252.3614723225014</v>
+        <v>277.0969401642774</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>30.25</v>
+        <v>31.15</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.7245006477125</v>
+        <v>50.85730366827963</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.945475292675</v>
+        <v>11.74088882969068</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9540475298993416</v>
+        <v>0.6655791190864601</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1592516386583748</v>
+        <v>0.07451700114774271</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6614</v>
+        <v>6803</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>248.0649621012034</v>
+        <v>274.0928879027684</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.3</v>
+        <v>267</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.92690982050217</v>
+        <v>41.8846567210084</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.30037518834754</v>
+        <v>20.80335167658852</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.329235798208224</v>
+        <v>0.8207950515756545</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0192269559523083</v>
+        <v>-0.0691633642214821</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6720</v>
+        <v>6584</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>240.6461930204765</v>
+        <v>268.7044976756221</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>126.5</v>
+        <v>531</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.89025069333286</v>
+        <v>40.08637355225412</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.48981234591869</v>
+        <v>18.81268364748185</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6155141166264398</v>
+        <v>0.5834847122589585</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.399658673222916</v>
+        <v>-4.292154626868065</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6680</v>
+        <v>6698</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>236.9772323097908</v>
+        <v>267.5446204947768</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>51.5</v>
+        <v>32.25</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>52.10221914005795</v>
+        <v>49.95343005350268</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>7.134259840672166</v>
+        <v>13.58149407281832</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>3.42319416091054</v>
+        <v>1.307107511488505</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>2.148762457308168</v>
+        <v>0.2222953765846546</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6823</v>
+        <v>6829</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>229.7352630078601</v>
+        <v>267.3459573926071</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>60.7</v>
+        <v>205</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.13346361901026</v>
+        <v>42.74788413417034</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.49077788827942</v>
+        <v>12.28141098610827</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.21066979064845</v>
+        <v>0.5229788857527479</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.353605748771723</v>
+        <v>-2.723933770198998</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6581</v>
+        <v>6556</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>229.3502177042413</v>
+        <v>259.7686138750226</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>108</v>
+        <v>61.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.92330387016325</v>
+        <v>50.01964891953681</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.5262100026807</v>
+        <v>7.793949599760867</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.9726772195457674</v>
+        <v>1.162475233687118</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2730758475084411</v>
+        <v>0.1914498444586813</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6625</v>
+        <v>6753</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>229.0300777639884</v>
+        <v>253.9791472728554</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.41548004810284</v>
+        <v>44.834659946935</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.29910658267998</v>
+        <v>10.4168013773926</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.881782436936116</v>
+        <v>0.4843935688369206</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0172662099888554</v>
+        <v>0.0869811078367925</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6477</v>
+        <v>6541</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>223.0562322552049</v>
+        <v>252.3614723225014</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>34.8</v>
+        <v>30.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.0889981855703</v>
+        <v>37.72450057699767</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.76312414285562</v>
+        <v>21.94547542081206</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6032454880694266</v>
+        <v>0.9540475298993416</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1262489209055989</v>
+        <v>0.1592516385025957</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6757</v>
+        <v>6581</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>221.6583903754</v>
+        <v>249.350217704241</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>53.4</v>
+        <v>108</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.96262719395464</v>
+        <v>41.92330347971117</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.93738057281285</v>
+        <v>16.52620978958325</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6254246613856866</v>
+        <v>0.9726772195457674</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0211868069649573</v>
+        <v>-0.2730758469520807</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6550</v>
+        <v>6614</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>215.2969854734521</v>
+        <v>248.0649621012034</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>17.5</v>
+        <v>35.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>80.90086807239881</v>
+        <v>40.9269097705158</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.02111451547541</v>
+        <v>17.30037526030435</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3497597817373697</v>
+        <v>0.329235798208224</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.9028496945602744</v>
+        <v>0.0192269559078028</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6517</v>
+        <v>6794</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>200.9586192628685</v>
+        <v>242.5778726835916</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>63.5</v>
+        <v>73.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.00072714795764</v>
+        <v>43.88363021336765</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.649044876120024</v>
+        <v>15.52369140576117</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.2500690775519916</v>
+        <v>0.9620573859630254</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0935530285553782</v>
+        <v>-0.3955058542807928</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6788</v>
+        <v>6720</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>198.003034519508</v>
+        <v>240.6461930204765</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>346.5</v>
+        <v>126.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>51.17283957388119</v>
+        <v>49.89025068709336</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.82535157274601</v>
+        <v>15.48981244012807</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6883770221731007</v>
+        <v>0.6155141166264398</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>2.205716396961548</v>
+        <v>1.399658673222916</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6573</v>
+        <v>6680</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>193.3683451596279</v>
+        <v>236.9772323097908</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16.3</v>
+        <v>51.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.98015381633848</v>
+        <v>52.10221933622357</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.93045047862789</v>
+        <v>7.134260478316494</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4923296513293496</v>
+        <v>3.42319416091054</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0719671652146489</v>
+        <v>2.148762441908216</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6515</v>
+        <v>6625</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>184.2728942637029</v>
+        <v>229.0300777639878</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>5770</v>
+        <v>74</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.37053523533661</v>
+        <v>41.41547941631897</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.87758401865018</v>
+        <v>12.29910660162857</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6463517088173263</v>
+        <v>0.881782436936116</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-74.80199575111848</v>
+        <v>0.0172662100556277</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6624</v>
+        <v>6477</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>172.5067342624708</v>
+        <v>223.0562322552049</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>38</v>
+        <v>34.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.43575364626667</v>
+        <v>49.08899839251997</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5.856628420268062</v>
+        <v>17.76312413043376</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.88288170258605</v>
+        <v>0.6032454880694266</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.334923102716718</v>
+        <v>0.1262489209834928</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6796</v>
+        <v>6757</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>158.6959459742276</v>
+        <v>221.6583903754</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.2475677090984</v>
+        <v>40.96262720816316</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>23.18401866333665</v>
+        <v>15.93738059224186</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2543796957155732</v>
+        <v>0.6254246613856866</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.216677318200424</v>
+        <v>0.0211868069649573</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6821</v>
+        <v>6573</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>156.1333239794247</v>
+        <v>213.3683451596279</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>42.25</v>
+        <v>16.3</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>53.56291220786687</v>
+        <v>46.98015380306214</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.52066970469891</v>
+        <v>17.93045040863045</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8641457317179769</v>
+        <v>0.4923296513293496</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.3262501869209233</v>
+        <v>0.0719671652146489</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6776</v>
+        <v>6517</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>155.8179909195328</v>
+        <v>200.9586192628685</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>52.8</v>
+        <v>63.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.84758382435644</v>
+        <v>46.00072699054266</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.54602121750209</v>
+        <v>9.649044900619865</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7516134609094086</v>
+        <v>0.2500690775519916</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1332869060682413</v>
+        <v>-0.09355302842184859</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6698</v>
+        <v>6515</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>152.5446204947751</v>
+        <v>184.2728942637033</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>32.25</v>
+        <v>5770</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>49.95342976011535</v>
+        <v>40.37053523533661</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.58149407103384</v>
+        <v>12.87758402957983</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.307107511488505</v>
+        <v>0.6463517088173263</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2222953766069068</v>
+        <v>-74.80199575000566</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6754</v>
+        <v>6498</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>135.2874338741327</v>
+        <v>173.0788105843295</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>41</v>
+        <v>68.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.46685143378325</v>
+        <v>45.41055279067778</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>9.033041510830987</v>
+        <v>15.4530337250195</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.343928850825544</v>
+        <v>0.5373006673758755</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.059853898843529</v>
+        <v>0.3525896482442983</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6790</v>
+        <v>6624</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>134.8378188420032</v>
+        <v>172.5067342624708</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>37.65</v>
+        <v>38</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.47800156621945</v>
+        <v>51.43575323900355</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.91439905749138</v>
+        <v>5.856628238261523</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.27242022648591</v>
+        <v>0.88288170258605</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.007839288404191199</v>
+        <v>0.3349231102609096</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6761</v>
+        <v>6776</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>134.5040349324438</v>
+        <v>155.8179909195331</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>164.5</v>
+        <v>52.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,25 +6753,25 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.75983674325573</v>
+        <v>51.84758398693209</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.76714005094293</v>
+        <v>15.54602097708727</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7151610103816961</v>
+        <v>0.7516134609094086</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.3699669759999677</v>
+        <v>0.1332869058234474</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6794</v>
+        <v>6722</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>132.5778726835916</v>
+        <v>143.4134378223873</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>73.2</v>
+        <v>32.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,25 +6806,25 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.88363004462308</v>
+        <v>46.45510759348073</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.52369118098444</v>
+        <v>18.14101496573799</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.9620573859630254</v>
+        <v>0.961886516450742</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3955058535686548</v>
+        <v>0.0177496804411073</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6722</v>
+        <v>6754</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>123.4134378223873</v>
+        <v>135.2874338741327</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>32.5</v>
+        <v>41</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.45510754073964</v>
+        <v>40.46685135255667</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.1410149256643</v>
+        <v>9.033041368269432</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.961886516450742</v>
+        <v>1.343928850825544</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0177496804188487</v>
+        <v>-0.0598538989770538</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6546</v>
+        <v>6582</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>123.2275640933278</v>
+        <v>135.0136820553431</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>59.7</v>
+        <v>31.3</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.34119657700973</v>
+        <v>47.00856931980569</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.81355635051306</v>
+        <v>13.96889623964588</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6204774116128376</v>
+        <v>0.2318135517687753</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0147453742834327</v>
+        <v>-0.0137744128630253</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6582</v>
+        <v>6790</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>115.0136820553435</v>
+        <v>134.8378188420032</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>31.3</v>
+        <v>37.65</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.00856954826234</v>
+        <v>41.47800147621673</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.96889601193984</v>
+        <v>12.91439907533238</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2318135517687753</v>
+        <v>1.27242022648591</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0137744128741515</v>
+        <v>0.007839288426441901</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6534</v>
+        <v>6761</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>91.51313416751942</v>
+        <v>134.5040349324439</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>90.8</v>
+        <v>164.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>48.20039912524474</v>
+        <v>43.7598368538342</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9.85400471826047</v>
+        <v>17.7671400646155</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.413366161639448</v>
+        <v>0.7151610103816961</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.08611696361583281</v>
+        <v>-0.3699669758219208</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6498</v>
+        <v>6546</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>58.07881058432945</v>
+        <v>123.2275640933278</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>68.3</v>
+        <v>59.7</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.41055286718101</v>
+        <v>46.34119660300399</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>15.45303369908169</v>
+        <v>16.81355643982087</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5373006673758755</v>
+        <v>0.6204774116128376</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,9 +7089,62 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.3525896480217598</v>
+        <v>-0.0147453746840082</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6534</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>正瀚-創</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>91.51313416751933</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>48.20039904603367</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>9.854004708717143</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.413366161639448</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0861169638161268</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
